--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\donid\Documents\Github\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAA281E-0678-44DA-813C-CE5C5C956709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7E6A3C-64EE-470C-8D2D-4513BA04D632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C98DD6CE-D6F2-4A74-ACC0-EB0522066C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C98DD6CE-D6F2-4A74-ACC0-EB0522066C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="2" r:id="rId1"/>
+    <sheet name="Formatting" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="A1xA12">Folha1!$D$6:$D$22</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
   <si>
     <t>Hello world</t>
   </si>
@@ -74,6 +75,27 @@
   <si>
     <t>Hello6</t>
   </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
 </sst>
 </file>
 
@@ -107,7 +129,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -115,15 +137,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3D545D-02F7-4FCB-A681-F8C5AAC2FC94}">
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:U97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="10.140625" bestFit="1" customWidth="1"/>
@@ -450,13 +512,7 @@
     <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="2">
-        <v>46315</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="1" spans="1:21">
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
@@ -482,11 +538,29 @@
         <v>8</v>
       </c>
       <c r="N1" s="3"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="2">
-        <v>46316</v>
-      </c>
+      <c r="O1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="D2" t="s">
         <v>10</v>
       </c>
@@ -508,10 +582,27 @@
       <c r="M2" s="3">
         <v>46303</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>20</v>
+      </c>
+      <c r="Q2">
+        <f>O2+P2</f>
+        <v>30</v>
+      </c>
+      <c r="R2">
+        <f>SUM(O2:Q2)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="2">
-        <v>46317</v>
+        <v>46315</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -534,10 +625,20 @@
       <c r="M3" s="3">
         <v>46304</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>20</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="0">O3+P3</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="2">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -560,8 +661,21 @@
       <c r="M4" s="3">
         <v>46305</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>30</v>
+      </c>
+      <c r="P4">
+        <v>40</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="2">
+        <v>46317</v>
+      </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
@@ -583,8 +697,21 @@
       <c r="M5" s="3">
         <v>46306</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>40</v>
+      </c>
+      <c r="P5">
+        <v>50</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="2">
+        <v>46318</v>
+      </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
@@ -603,8 +730,22 @@
       <c r="M6" s="3">
         <v>46307</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>50</v>
+      </c>
+      <c r="P6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="R6">
+        <f>SUM(P2:P11)</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="F7" t="s">
         <v>0</v>
       </c>
@@ -620,8 +761,18 @@
       <c r="M7" s="3">
         <v>46308</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>60</v>
+      </c>
+      <c r="P7">
+        <v>70</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="F8" t="s">
         <v>0</v>
       </c>
@@ -637,8 +788,18 @@
       <c r="M8" s="3">
         <v>46309</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>70</v>
+      </c>
+      <c r="P8">
+        <v>80</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="F9" t="s">
         <v>0</v>
       </c>
@@ -651,8 +812,18 @@
       <c r="M9" s="3">
         <v>46310</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>80</v>
+      </c>
+      <c r="P9">
+        <v>90</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="F10" t="s">
         <v>0</v>
       </c>
@@ -665,8 +836,18 @@
       <c r="M10" s="3">
         <v>46311</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>90</v>
+      </c>
+      <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="F11" t="s">
         <v>0</v>
       </c>
@@ -676,8 +857,18 @@
       <c r="M11" s="3">
         <v>46312</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>110</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="F12" t="s">
         <v>0</v>
       </c>
@@ -688,7 +879,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:21">
       <c r="F13" t="s">
         <v>0</v>
       </c>
@@ -699,7 +890,7 @@
         <v>46314</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:21">
       <c r="F14" t="s">
         <v>0</v>
       </c>
@@ -710,7 +901,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:21">
       <c r="F15" t="s">
         <v>0</v>
       </c>
@@ -721,7 +912,7 @@
         <v>46316</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:21">
       <c r="F16" t="s">
         <v>0</v>
       </c>
@@ -1237,6 +1428,1225 @@
     <row r="97" spans="13:13">
       <c r="M97" s="3">
         <v>46398</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5277451C-FDB8-4F0F-B651-1CAA771BDF19}">
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>33</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>38</v>
+      </c>
+      <c r="C8">
+        <v>39</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>43</v>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>47</v>
+      </c>
+      <c r="F9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>49</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>51</v>
+      </c>
+      <c r="D10">
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>56</v>
+      </c>
+      <c r="C11">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>58</v>
+      </c>
+      <c r="E11">
+        <v>59</v>
+      </c>
+      <c r="F11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>62</v>
+      </c>
+      <c r="C12">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>64</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+      <c r="F12">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>67</v>
+      </c>
+      <c r="B13">
+        <v>68</v>
+      </c>
+      <c r="C13">
+        <v>69</v>
+      </c>
+      <c r="D13">
+        <v>70</v>
+      </c>
+      <c r="E13">
+        <v>71</v>
+      </c>
+      <c r="F13">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>73</v>
+      </c>
+      <c r="B14">
+        <v>74</v>
+      </c>
+      <c r="C14">
+        <v>75</v>
+      </c>
+      <c r="D14">
+        <v>76</v>
+      </c>
+      <c r="E14">
+        <v>77</v>
+      </c>
+      <c r="F14">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>79</v>
+      </c>
+      <c r="B15">
+        <v>80</v>
+      </c>
+      <c r="C15">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <v>82</v>
+      </c>
+      <c r="E15">
+        <v>83</v>
+      </c>
+      <c r="F15">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>85</v>
+      </c>
+      <c r="B16">
+        <v>86</v>
+      </c>
+      <c r="C16">
+        <v>87</v>
+      </c>
+      <c r="D16">
+        <v>88</v>
+      </c>
+      <c r="E16">
+        <v>89</v>
+      </c>
+      <c r="F16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>91</v>
+      </c>
+      <c r="B17">
+        <v>92</v>
+      </c>
+      <c r="C17">
+        <v>93</v>
+      </c>
+      <c r="D17">
+        <v>94</v>
+      </c>
+      <c r="E17">
+        <v>95</v>
+      </c>
+      <c r="F17">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>97</v>
+      </c>
+      <c r="B18">
+        <v>98</v>
+      </c>
+      <c r="C18">
+        <v>99</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>101</v>
+      </c>
+      <c r="F18">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>103</v>
+      </c>
+      <c r="B19">
+        <v>104</v>
+      </c>
+      <c r="C19">
+        <v>105</v>
+      </c>
+      <c r="D19">
+        <v>106</v>
+      </c>
+      <c r="E19">
+        <v>107</v>
+      </c>
+      <c r="F19">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>109</v>
+      </c>
+      <c r="B20">
+        <v>110</v>
+      </c>
+      <c r="C20">
+        <v>111</v>
+      </c>
+      <c r="D20">
+        <v>112</v>
+      </c>
+      <c r="E20">
+        <v>113</v>
+      </c>
+      <c r="F20">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>115</v>
+      </c>
+      <c r="B21">
+        <v>116</v>
+      </c>
+      <c r="C21">
+        <v>117</v>
+      </c>
+      <c r="D21">
+        <v>118</v>
+      </c>
+      <c r="E21">
+        <v>119</v>
+      </c>
+      <c r="F21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>121</v>
+      </c>
+      <c r="B22">
+        <v>122</v>
+      </c>
+      <c r="C22">
+        <v>123</v>
+      </c>
+      <c r="D22">
+        <v>124</v>
+      </c>
+      <c r="E22">
+        <v>125</v>
+      </c>
+      <c r="F22">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>127</v>
+      </c>
+      <c r="B23">
+        <v>128</v>
+      </c>
+      <c r="C23">
+        <v>129</v>
+      </c>
+      <c r="D23">
+        <v>130</v>
+      </c>
+      <c r="E23">
+        <v>131</v>
+      </c>
+      <c r="F23">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>133</v>
+      </c>
+      <c r="B24">
+        <v>134</v>
+      </c>
+      <c r="C24">
+        <v>135</v>
+      </c>
+      <c r="D24">
+        <v>136</v>
+      </c>
+      <c r="E24">
+        <v>137</v>
+      </c>
+      <c r="F24">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>139</v>
+      </c>
+      <c r="B25">
+        <v>140</v>
+      </c>
+      <c r="C25">
+        <v>141</v>
+      </c>
+      <c r="D25">
+        <v>142</v>
+      </c>
+      <c r="E25">
+        <v>143</v>
+      </c>
+      <c r="F25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>145</v>
+      </c>
+      <c r="B26">
+        <v>146</v>
+      </c>
+      <c r="C26">
+        <v>147</v>
+      </c>
+      <c r="D26">
+        <v>148</v>
+      </c>
+      <c r="E26">
+        <v>149</v>
+      </c>
+      <c r="F26">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>151</v>
+      </c>
+      <c r="B27">
+        <v>152</v>
+      </c>
+      <c r="C27">
+        <v>153</v>
+      </c>
+      <c r="D27">
+        <v>154</v>
+      </c>
+      <c r="E27">
+        <v>155</v>
+      </c>
+      <c r="F27">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>157</v>
+      </c>
+      <c r="B28">
+        <v>158</v>
+      </c>
+      <c r="C28">
+        <v>159</v>
+      </c>
+      <c r="D28">
+        <v>160</v>
+      </c>
+      <c r="E28">
+        <v>161</v>
+      </c>
+      <c r="F28">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>163</v>
+      </c>
+      <c r="B29">
+        <v>164</v>
+      </c>
+      <c r="C29">
+        <v>165</v>
+      </c>
+      <c r="D29">
+        <v>166</v>
+      </c>
+      <c r="E29">
+        <v>167</v>
+      </c>
+      <c r="F29">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>169</v>
+      </c>
+      <c r="B30">
+        <v>170</v>
+      </c>
+      <c r="C30">
+        <v>171</v>
+      </c>
+      <c r="D30">
+        <v>172</v>
+      </c>
+      <c r="E30">
+        <v>173</v>
+      </c>
+      <c r="F30">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>175</v>
+      </c>
+      <c r="B31">
+        <v>176</v>
+      </c>
+      <c r="C31">
+        <v>177</v>
+      </c>
+      <c r="D31">
+        <v>178</v>
+      </c>
+      <c r="E31">
+        <v>179</v>
+      </c>
+      <c r="F31">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>181</v>
+      </c>
+      <c r="B32">
+        <v>182</v>
+      </c>
+      <c r="C32">
+        <v>183</v>
+      </c>
+      <c r="D32">
+        <v>184</v>
+      </c>
+      <c r="E32">
+        <v>185</v>
+      </c>
+      <c r="F32">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>187</v>
+      </c>
+      <c r="B33">
+        <v>188</v>
+      </c>
+      <c r="C33">
+        <v>189</v>
+      </c>
+      <c r="D33">
+        <v>190</v>
+      </c>
+      <c r="E33">
+        <v>191</v>
+      </c>
+      <c r="F33">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>193</v>
+      </c>
+      <c r="B34">
+        <v>194</v>
+      </c>
+      <c r="C34">
+        <v>195</v>
+      </c>
+      <c r="D34">
+        <v>196</v>
+      </c>
+      <c r="E34">
+        <v>197</v>
+      </c>
+      <c r="F34">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>199</v>
+      </c>
+      <c r="B35">
+        <v>200</v>
+      </c>
+      <c r="C35">
+        <v>201</v>
+      </c>
+      <c r="D35">
+        <v>202</v>
+      </c>
+      <c r="E35">
+        <v>203</v>
+      </c>
+      <c r="F35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>205</v>
+      </c>
+      <c r="B36">
+        <v>206</v>
+      </c>
+      <c r="C36">
+        <v>207</v>
+      </c>
+      <c r="D36">
+        <v>208</v>
+      </c>
+      <c r="E36">
+        <v>209</v>
+      </c>
+      <c r="F36">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>211</v>
+      </c>
+      <c r="B37">
+        <v>212</v>
+      </c>
+      <c r="C37">
+        <v>213</v>
+      </c>
+      <c r="D37">
+        <v>214</v>
+      </c>
+      <c r="E37">
+        <v>215</v>
+      </c>
+      <c r="F37">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>217</v>
+      </c>
+      <c r="B38">
+        <v>218</v>
+      </c>
+      <c r="C38">
+        <v>219</v>
+      </c>
+      <c r="D38">
+        <v>220</v>
+      </c>
+      <c r="E38">
+        <v>221</v>
+      </c>
+      <c r="F38">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>223</v>
+      </c>
+      <c r="B39">
+        <v>224</v>
+      </c>
+      <c r="C39">
+        <v>225</v>
+      </c>
+      <c r="D39">
+        <v>226</v>
+      </c>
+      <c r="E39">
+        <v>227</v>
+      </c>
+      <c r="F39">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>229</v>
+      </c>
+      <c r="B40">
+        <v>230</v>
+      </c>
+      <c r="C40">
+        <v>231</v>
+      </c>
+      <c r="D40">
+        <v>232</v>
+      </c>
+      <c r="E40">
+        <v>233</v>
+      </c>
+      <c r="F40">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>235</v>
+      </c>
+      <c r="B41">
+        <v>236</v>
+      </c>
+      <c r="C41">
+        <v>237</v>
+      </c>
+      <c r="D41">
+        <v>238</v>
+      </c>
+      <c r="E41">
+        <v>239</v>
+      </c>
+      <c r="F41">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>241</v>
+      </c>
+      <c r="B42">
+        <v>242</v>
+      </c>
+      <c r="C42">
+        <v>243</v>
+      </c>
+      <c r="D42">
+        <v>244</v>
+      </c>
+      <c r="E42">
+        <v>245</v>
+      </c>
+      <c r="F42">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>247</v>
+      </c>
+      <c r="B43">
+        <v>248</v>
+      </c>
+      <c r="C43">
+        <v>249</v>
+      </c>
+      <c r="D43">
+        <v>250</v>
+      </c>
+      <c r="E43">
+        <v>251</v>
+      </c>
+      <c r="F43">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>253</v>
+      </c>
+      <c r="B44">
+        <v>254</v>
+      </c>
+      <c r="C44">
+        <v>255</v>
+      </c>
+      <c r="D44">
+        <v>256</v>
+      </c>
+      <c r="E44">
+        <v>257</v>
+      </c>
+      <c r="F44">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>259</v>
+      </c>
+      <c r="B45">
+        <v>260</v>
+      </c>
+      <c r="C45">
+        <v>261</v>
+      </c>
+      <c r="D45">
+        <v>262</v>
+      </c>
+      <c r="E45">
+        <v>263</v>
+      </c>
+      <c r="F45">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>265</v>
+      </c>
+      <c r="B46">
+        <v>266</v>
+      </c>
+      <c r="C46">
+        <v>267</v>
+      </c>
+      <c r="D46">
+        <v>268</v>
+      </c>
+      <c r="E46">
+        <v>269</v>
+      </c>
+      <c r="F46">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>271</v>
+      </c>
+      <c r="B47">
+        <v>272</v>
+      </c>
+      <c r="C47">
+        <v>273</v>
+      </c>
+      <c r="D47">
+        <v>274</v>
+      </c>
+      <c r="E47">
+        <v>275</v>
+      </c>
+      <c r="F47">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>277</v>
+      </c>
+      <c r="B48">
+        <v>278</v>
+      </c>
+      <c r="C48">
+        <v>279</v>
+      </c>
+      <c r="D48">
+        <v>280</v>
+      </c>
+      <c r="E48">
+        <v>281</v>
+      </c>
+      <c r="F48">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>283</v>
+      </c>
+      <c r="B49">
+        <v>284</v>
+      </c>
+      <c r="C49">
+        <v>285</v>
+      </c>
+      <c r="D49">
+        <v>286</v>
+      </c>
+      <c r="E49">
+        <v>287</v>
+      </c>
+      <c r="F49">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>289</v>
+      </c>
+      <c r="B50">
+        <v>290</v>
+      </c>
+      <c r="C50">
+        <v>291</v>
+      </c>
+      <c r="D50">
+        <v>292</v>
+      </c>
+      <c r="E50">
+        <v>293</v>
+      </c>
+      <c r="F50">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>295</v>
+      </c>
+      <c r="B51">
+        <v>296</v>
+      </c>
+      <c r="C51">
+        <v>297</v>
+      </c>
+      <c r="D51">
+        <v>298</v>
+      </c>
+      <c r="E51">
+        <v>299</v>
+      </c>
+      <c r="F51">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>301</v>
+      </c>
+      <c r="B52">
+        <v>302</v>
+      </c>
+      <c r="C52">
+        <v>303</v>
+      </c>
+      <c r="D52">
+        <v>304</v>
+      </c>
+      <c r="E52">
+        <v>305</v>
+      </c>
+      <c r="F52">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>307</v>
+      </c>
+      <c r="B53">
+        <v>308</v>
+      </c>
+      <c r="C53">
+        <v>309</v>
+      </c>
+      <c r="D53">
+        <v>310</v>
+      </c>
+      <c r="E53">
+        <v>311</v>
+      </c>
+      <c r="F53">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>313</v>
+      </c>
+      <c r="B54">
+        <v>314</v>
+      </c>
+      <c r="C54">
+        <v>315</v>
+      </c>
+      <c r="D54">
+        <v>316</v>
+      </c>
+      <c r="E54">
+        <v>317</v>
+      </c>
+      <c r="F54">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>319</v>
+      </c>
+      <c r="B55">
+        <v>320</v>
+      </c>
+      <c r="C55">
+        <v>321</v>
+      </c>
+      <c r="D55">
+        <v>322</v>
+      </c>
+      <c r="E55">
+        <v>323</v>
+      </c>
+      <c r="F55">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>325</v>
+      </c>
+      <c r="B56">
+        <v>326</v>
+      </c>
+      <c r="C56">
+        <v>327</v>
+      </c>
+      <c r="D56">
+        <v>328</v>
+      </c>
+      <c r="E56">
+        <v>329</v>
+      </c>
+      <c r="F56">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>331</v>
+      </c>
+      <c r="B57">
+        <v>332</v>
+      </c>
+      <c r="C57">
+        <v>333</v>
+      </c>
+      <c r="D57">
+        <v>334</v>
+      </c>
+      <c r="E57">
+        <v>335</v>
+      </c>
+      <c r="F57">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>337</v>
+      </c>
+      <c r="B58">
+        <v>338</v>
+      </c>
+      <c r="C58">
+        <v>339</v>
+      </c>
+      <c r="D58">
+        <v>340</v>
+      </c>
+      <c r="E58">
+        <v>341</v>
+      </c>
+      <c r="F58">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>343</v>
+      </c>
+      <c r="B59">
+        <v>344</v>
+      </c>
+      <c r="C59">
+        <v>345</v>
+      </c>
+      <c r="D59">
+        <v>346</v>
+      </c>
+      <c r="E59">
+        <v>347</v>
+      </c>
+      <c r="F59">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>349</v>
+      </c>
+      <c r="B60">
+        <v>350</v>
+      </c>
+      <c r="C60">
+        <v>351</v>
+      </c>
+      <c r="D60">
+        <v>352</v>
+      </c>
+      <c r="E60">
+        <v>353</v>
+      </c>
+      <c r="F60">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
